--- a/docs/test-data/attendance-import.xlsx
+++ b/docs/test-data/attendance-import.xlsx
@@ -429,9 +429,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-    </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -446,40 +444,36 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr"/>
-    </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>STEP 1 - replace the placeholder</t>
+          <t>STEP 1 - no setup needed</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Edit &gt; Find and Select &gt; Replace: REPLACE_WITH_SECTION_UUID</t>
+          <t xml:space="preserve">   The section is written by name: Grade 8 - Bonifacio.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">   with the UUID of the section the student is enrolled in.</t>
+          <t xml:space="preserve">   Student AEGIS-QA-S0026 is enrolled in that section.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Student AEGIS-QA-S0026 is in Grade 8 - Bonifacio (see README.md for where to copy it).</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr"/>
-    </row>
+          <t xml:space="preserve">   Student AEGIS-QA-S0026 is enrolled in that section.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
@@ -508,9 +502,7 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr"/>
-    </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
@@ -546,27 +538,25 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr"/>
-    </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>STEP 4 - duplicate test (optional)</t>
+          <t>STEP 4 - re-upload test (optional)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Import Valid Attendance a second time: every row is rejected and</t>
+          <t xml:space="preserve">   Import Valid Attendance a second time: the same 5 rows</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">   reported as an existing record for that student and date.</t>
+          <t xml:space="preserve">   succeed again and update the existing records in place.</t>
         </is>
       </c>
     </row>
@@ -614,7 +604,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>REPLACE_WITH_SECTION_UUID</t>
+          <t>Grade 8 - Bonifacio</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -636,7 +626,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>REPLACE_WITH_SECTION_UUID</t>
+          <t>Grade 8 - Bonifacio</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -658,7 +648,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>REPLACE_WITH_SECTION_UUID</t>
+          <t>Grade 8 - Bonifacio</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -680,7 +670,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>REPLACE_WITH_SECTION_UUID</t>
+          <t>Grade 8 - Bonifacio</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -702,7 +692,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>REPLACE_WITH_SECTION_UUID</t>
+          <t>Grade 8 - Bonifacio</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -760,7 +750,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>REPLACE_WITH_SECTION_UUID</t>
+          <t>Grade 8 - Bonifacio</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -782,7 +772,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>REPLACE_WITH_SECTION_UUID</t>
+          <t>Grade 8 - Bonifacio</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -804,7 +794,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>REPLACE_WITH_SECTION_UUID</t>
+          <t>Grade 8 - Bonifacio</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -826,7 +816,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>REPLACE_WITH_SECTION_UUID</t>
+          <t>Grade 8 - Bonifacio</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -846,7 +836,6 @@
           <t>AEGIS-QA-S0026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>2026-06-15</t>
